--- a/data/sample_cap_table.xlsx
+++ b/data/sample_cap_table.xlsx
@@ -55,7 +55,7 @@
     <t>Note</t>
   </si>
   <si>
-    <t>Common (Type of Time-Based)</t>
+    <t>Common</t>
   </si>
   <si>
     <t>Security A</t>
@@ -562,8 +562,8 @@
         <v>0.0</v>
       </c>
       <c r="N2" s="5" t="str">
-        <f t="shared" ref="N2:N16" si="2">A2&amp;" - "&amp;IF(C2=1,"Time-Based Vesting",IF(M2=1,"Performance-Based Vesting (Cliff)","Performance-Based Vesting (Linear)"))&amp;IF(E2&gt;0,", "&amp;E2&amp;" Tranche(s) Vesting "&amp;IF(F2&gt;0,"@ "&amp;F2&amp;"x","")&amp;IF(G2&gt;0," / "&amp;G2&amp;"x","")&amp;IF(H2&gt;0," / "&amp;H2&amp;"x","")&amp;", with vesting schedule of "&amp;IF(I2&gt;=0,ROUND(I2*100,0)&amp;"%", "")&amp;IF(J2&gt;=0," / "&amp;ROUND(J2*100,0)&amp;"%", "")&amp;IF(K2&gt;=0," / "&amp;ROUND(K2*100,0)&amp;"%", ""),"")</f>
-        <v>Common (Type of Time-Based) - Time-Based Vesting</v>
+        <f t="shared" ref="N2:N16" si="2">A2&amp;" - "&amp;IF(C2=1,"Time-Based",IF(M2=1,"Performance-Based (Cliff)","Performance-Based (Linear)"))&amp;IF(E2&gt;0,", "&amp;E2&amp;" Tranche(s) Vesting "&amp;IF(F2&gt;0,"@ $"&amp;F2,"")&amp;IF(G2&gt;0," / $"&amp;G2,"")&amp;IF(H2&gt;0," / $"&amp;H2,"")&amp;" for "&amp;IF(I2&gt;=0,ROUND(I2*100,0)&amp;"%", "")&amp;IF(J2&gt;=0," / "&amp;ROUND(J2*100,0)&amp;"%", "")&amp;IF(K2&gt;=0," / "&amp;ROUND(K2*100,0)&amp;"%", ""),"")</f>
+        <v>Common - Time-Based</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
@@ -609,7 +609,7 @@
       </c>
       <c r="N3" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>Security A - Time-Based Vesting</v>
+        <v>Security A - Time-Based</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
@@ -655,7 +655,7 @@
       </c>
       <c r="N4" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>Security B - Performance-Based Vesting (Cliff), 2 Tranche(s) Vesting @ 20x / 30x, with vesting schedule of 50% / 100%</v>
+        <v>Security B - Performance-Based (Cliff), 2 Tranche(s) Vesting @ $20 / $30 for 50% / 100%</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
@@ -701,7 +701,7 @@
       </c>
       <c r="N5" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>Security C - Performance-Based Vesting (Linear), 2 Tranche(s) Vesting @ 20x / 30x, with vesting schedule of 50% / 100%</v>
+        <v>Security C - Performance-Based (Linear), 2 Tranche(s) Vesting @ $20 / $30 for 50% / 100%</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
@@ -747,7 +747,7 @@
       </c>
       <c r="N6" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>Security D - Time-Based Vesting</v>
+        <v>Security D - Time-Based</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
@@ -793,7 +793,7 @@
       </c>
       <c r="N7" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>Security E - Performance-Based Vesting (Cliff), 3 Tranche(s) Vesting @ 30x / 40x / 50x, with vesting schedule of 50% / 75% / 100%</v>
+        <v>Security E - Performance-Based (Cliff), 3 Tranche(s) Vesting @ $30 / $40 / $50 for 50% / 75% / 100%</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
@@ -839,7 +839,7 @@
       </c>
       <c r="N8" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>Security F - Performance-Based Vesting (Linear), 3 Tranche(s) Vesting @ 30x / 40x / 50x, with vesting schedule of 50% / 75% / 100%</v>
+        <v>Security F - Performance-Based (Linear), 3 Tranche(s) Vesting @ $30 / $40 / $50 for 50% / 75% / 100%</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
@@ -885,7 +885,7 @@
       </c>
       <c r="N9" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>Security G - Performance-Based Vesting (Cliff), 1 Tranche(s) Vesting @ 30x, with vesting schedule of 100%</v>
+        <v>Security G - Performance-Based (Cliff), 1 Tranche(s) Vesting @ $30 for 100%</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
@@ -931,7 +931,7 @@
       </c>
       <c r="N10" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>Security H - Performance-Based Vesting (Cliff), 1 Tranche(s) Vesting @ 40x, with vesting schedule of 100%</v>
+        <v>Security H - Performance-Based (Cliff), 1 Tranche(s) Vesting @ $40 for 100%</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
@@ -977,7 +977,7 @@
       </c>
       <c r="N11" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>Security I - Performance-Based Vesting (Cliff), 1 Tranche(s) Vesting @ 30x, with vesting schedule of 100%</v>
+        <v>Security I - Performance-Based (Cliff), 1 Tranche(s) Vesting @ $30 for 100%</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="N12" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>Security J - Performance-Based Vesting (Cliff), 1 Tranche(s) Vesting @ 40x, with vesting schedule of 100%</v>
+        <v>Security J - Performance-Based (Cliff), 1 Tranche(s) Vesting @ $40 for 100%</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="N13" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>Security K - Performance-Based Vesting (Cliff), 2 Tranche(s) Vesting @ 30x / 40x, with vesting schedule of 0% / 100%</v>
+        <v>Security K - Performance-Based (Cliff), 2 Tranche(s) Vesting @ $30 / $40 for 0% / 100%</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="N14" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>Security L - Performance-Based Vesting (Linear), 2 Tranche(s) Vesting @ 30x / 40x, with vesting schedule of 0% / 100%</v>
+        <v>Security L - Performance-Based (Linear), 2 Tranche(s) Vesting @ $30 / $40 for 0% / 100%</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="N15" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>Security M - Performance-Based Vesting (Cliff), 3 Tranche(s) Vesting @ 10x / 25x / 40x, with vesting schedule of 33% / 67% / 100%</v>
+        <v>Security M - Performance-Based (Cliff), 3 Tranche(s) Vesting @ $10 / $25 / $40 for 33% / 67% / 100%</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="N16" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>Security N - Performance-Based Vesting (Linear), 3 Tranche(s) Vesting @ 10x / 25x / 40x, with vesting schedule of 33% / 67% / 100%</v>
+        <v>Security N - Performance-Based (Linear), 3 Tranche(s) Vesting @ $10 / $25 / $40 for 33% / 67% / 100%</v>
       </c>
     </row>
   </sheetData>
